--- a/PythonScript/EEG算法测试清单.xlsx
+++ b/PythonScript/EEG算法测试清单.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git\tms-eeg-algorithms\eeg-algorithm\PythonScript\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="在线算法" sheetId="1" r:id="rId1"/>
     <sheet name="离线算法" sheetId="2" r:id="rId2"/>
     <sheet name="公共算法" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="138">
   <si>
     <t>序号</t>
   </si>
@@ -433,19 +433,33 @@
   </si>
   <si>
     <t>电极数 &lt; 3 或无坐标报错；网格尺寸 ≥ 8x8；插值光滑、头外 NaN。</t>
+  </si>
+  <si>
+    <t>是</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>可行</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>可行</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>是</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>可行</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="22">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -462,158 +476,21 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -626,194 +503,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -821,253 +512,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1078,65 +527,298 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>48164</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>342578</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>847725</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="图片 1"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="16402050" y="1286414"/>
+          <a:ext cx="1695128" cy="799561"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>28574</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>770014</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>599049</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>819575</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="图片 2"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="16411574" y="4580014"/>
+          <a:ext cx="3313675" cy="906811"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>47625</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>232243</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>402559</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>827033</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="图片 3"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="16430625" y="232243"/>
+          <a:ext cx="1040734" cy="975790"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>657225</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>761253</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>124805</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>848333</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="图片 4"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="16354425" y="2856753"/>
+          <a:ext cx="1524980" cy="944330"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>171449</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>774988</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>249286</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>753115</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="图片 5"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="17926049" y="2870488"/>
+          <a:ext cx="2135237" cy="835377"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>238125</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>755789</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>382673</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>61978</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="图片 6"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="16621125" y="2851289"/>
+          <a:ext cx="2887748" cy="1020689"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>323850</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>745352</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>382659</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>29166</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="图片 7"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="19450050" y="2840852"/>
+          <a:ext cx="2802009" cy="998314"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1418,14 +1100,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
@@ -1435,7 +1117,7 @@
     <col min="6" max="6" width="48" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:8">
+    <row r="1" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1461,7 +1143,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" ht="68" customHeight="1" spans="1:8">
+    <row r="2" spans="1:8" ht="68.099999999999994" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -1481,7 +1163,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" ht="68" customHeight="1" spans="1:8">
+    <row r="3" spans="1:8" ht="68.099999999999994" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -1501,7 +1183,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" ht="68" customHeight="1" spans="1:8">
+    <row r="4" spans="1:8" ht="68.099999999999994" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -1521,7 +1203,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" ht="68" customHeight="1" spans="1:8">
+    <row r="5" spans="1:8" ht="68.099999999999994" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -1544,7 +1226,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" ht="68" customHeight="1" spans="1:8">
+    <row r="6" spans="1:8" ht="68.099999999999994" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -1567,7 +1249,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" ht="68" customHeight="1" spans="1:8">
+    <row r="7" spans="1:8" ht="68.099999999999994" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -1590,7 +1272,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="8" ht="68" customHeight="1" spans="1:8">
+    <row r="8" spans="1:8" ht="68.099999999999994" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -1610,7 +1292,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="9" ht="68" customHeight="1" spans="1:8">
+    <row r="9" spans="1:8" ht="68.099999999999994" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -1631,16 +1313,15 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H16"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
@@ -1650,7 +1331,7 @@
     <col min="6" max="6" width="48" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:8">
+    <row r="1" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1676,7 +1357,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" ht="68" customHeight="1" spans="1:8">
+    <row r="2" spans="1:8" ht="68.099999999999994" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -1695,8 +1376,14 @@
       <c r="F2" s="3" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="3" ht="68" customHeight="1" spans="1:8">
+      <c r="G2" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="68.099999999999994" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -1715,8 +1402,14 @@
       <c r="F3" s="3" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="4" ht="68" customHeight="1" spans="1:8">
+      <c r="G3" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="68.099999999999994" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -1739,7 +1432,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="5" ht="68" customHeight="1" spans="1:8">
+    <row r="5" spans="1:8" ht="68.099999999999994" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -1758,8 +1451,14 @@
       <c r="F5" s="3" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="6" ht="68" customHeight="1" spans="1:8">
+      <c r="G5" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="68.099999999999994" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -1779,7 +1478,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="7" ht="68" customHeight="1" spans="1:8">
+    <row r="7" spans="1:8" ht="68.099999999999994" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -1798,8 +1497,14 @@
       <c r="F7" s="3" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="8" ht="68" customHeight="1" spans="1:8">
+      <c r="G7" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="68.099999999999994" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -1822,7 +1527,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="9" ht="68" customHeight="1" spans="1:8">
+    <row r="9" spans="1:8" ht="68.099999999999994" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -1845,7 +1550,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="10" ht="68" customHeight="1" spans="1:8">
+    <row r="10" spans="1:8" ht="68.099999999999994" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -1868,7 +1573,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="11" ht="68" customHeight="1" spans="1:8">
+    <row r="11" spans="1:8" ht="68.099999999999994" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -1891,7 +1596,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="12" ht="68" customHeight="1" spans="1:8">
+    <row r="12" spans="1:8" ht="68.099999999999994" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -1914,7 +1619,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="13" ht="68" customHeight="1" spans="1:8">
+    <row r="13" spans="1:8" ht="68.099999999999994" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -1937,7 +1642,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="14" ht="68" customHeight="1" spans="1:8">
+    <row r="14" spans="1:8" ht="68.099999999999994" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -1957,7 +1662,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="15" ht="68" customHeight="1" spans="1:8">
+    <row r="15" spans="1:8" ht="68.099999999999994" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -1977,7 +1682,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="16" ht="68" customHeight="1" spans="1:8">
+    <row r="16" spans="1:8" ht="68.099999999999994" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -2001,16 +1706,17 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="3" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
@@ -2020,7 +1726,7 @@
     <col min="6" max="6" width="48" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:8">
+    <row r="1" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2046,7 +1752,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" ht="68" customHeight="1" spans="1:8">
+    <row r="2" spans="1:8" ht="68.099999999999994" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -2066,7 +1772,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="3" ht="68" customHeight="1" spans="1:8">
+    <row r="3" spans="1:8" ht="68.099999999999994" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -2086,7 +1792,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="4" ht="68" customHeight="1" spans="1:8">
+    <row r="4" spans="1:8" ht="68.099999999999994" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -2107,7 +1813,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/PythonScript/EEG算法测试清单.xlsx
+++ b/PythonScript/EEG算法测试清单.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Desktop\eeg-algorithm\PythonScript\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="27945" windowHeight="12255"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="27945" windowHeight="12255" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="在线算法" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="142">
   <si>
     <t>序号</t>
   </si>
@@ -452,6 +452,22 @@
   </si>
   <si>
     <t>可行</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>可行</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>是</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>是</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>算法还需优化</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -472,12 +488,14 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -516,7 +534,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -532,6 +550,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -810,6 +831,82 @@
         <a:xfrm>
           <a:off x="19450050" y="2840852"/>
           <a:ext cx="2802009" cy="998314"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>844370</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>1682</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>839274</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="图片 8"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="16421100" y="2082620"/>
+          <a:ext cx="1335182" cy="852154"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>85725</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>774633</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>630360</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>839022</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="图片 9"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="16468725" y="3727383"/>
+          <a:ext cx="1916235" cy="921639"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1428,8 +1525,11 @@
       <c r="F4" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="G4" t="s">
-        <v>61</v>
+      <c r="G4" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="68.099999999999994" customHeight="1" x14ac:dyDescent="0.15">
@@ -1476,6 +1576,12 @@
       </c>
       <c r="F6" s="3" t="s">
         <v>71</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="68.099999999999994" customHeight="1" x14ac:dyDescent="0.15">

--- a/PythonScript/EEG算法测试清单.xlsx
+++ b/PythonScript/EEG算法测试清单.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="147">
   <si>
     <t>序号</t>
   </si>
@@ -439,26 +439,10 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>可行</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>可行</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>是</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>可行</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>可行</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>是</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -467,7 +451,124 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>是</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>是</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>可行（采用原始数据与滤波去除伪造后数据对比频谱效果，效果有差异）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>可行（采用预处理后数据已去除30hz以上，gamma地形图低验证合理）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>可行（通过滤除后频谱相应验证：高通采用5hz，低通</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>20，带通5-20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>可行（50hz工频去除）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>可行（采用6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>4导数据验证重参考计算效果</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>可行（5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>0hz降到20hz可行</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>算法还需优化</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>可行（对比原始与asr去除效果</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）具备去伪迹效果</t>
+    </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -652,15 +753,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>47625</xdr:colOff>
+      <xdr:colOff>47624</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>232243</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>402559</xdr:colOff>
+      <xdr:colOff>414469</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>827033</xdr:rowOff>
+      <xdr:rowOff>838201</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -677,8 +778,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="16430625" y="232243"/>
-          <a:ext cx="1040734" cy="975790"/>
+          <a:off x="16430624" y="232243"/>
+          <a:ext cx="1052645" cy="986958"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -689,16 +790,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>657225</xdr:colOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>761253</xdr:rowOff>
+      <xdr:rowOff>751728</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>124805</xdr:colOff>
+      <xdr:colOff>162905</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>848333</xdr:rowOff>
+      <xdr:rowOff>838808</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -715,7 +816,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="16354425" y="2856753"/>
+          <a:off x="17649825" y="2847228"/>
           <a:ext cx="1524980" cy="944330"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -907,6 +1008,82 @@
         <a:xfrm>
           <a:off x="16468725" y="3727383"/>
           <a:ext cx="1916235" cy="921639"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>28575</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>551230</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>11103</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>819670</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="图片 10"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="16411575" y="10361980"/>
+          <a:ext cx="3411528" cy="1125690"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>745340</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>439209</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>248409</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="图片 11"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="16497300" y="11413340"/>
+          <a:ext cx="1696509" cy="1217569"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1426,6 +1603,7 @@
     <col min="4" max="4" width="52" customWidth="1"/>
     <col min="5" max="5" width="36" customWidth="1"/>
     <col min="6" max="6" width="48" customWidth="1"/>
+    <col min="8" max="8" width="25.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.15">
@@ -1476,8 +1654,8 @@
       <c r="G2" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="H2" s="4" t="s">
-        <v>134</v>
+      <c r="H2" s="5" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="68.099999999999994" customHeight="1" x14ac:dyDescent="0.15">
@@ -1503,7 +1681,7 @@
         <v>133</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="68.099999999999994" customHeight="1" x14ac:dyDescent="0.15">
@@ -1526,10 +1704,10 @@
         <v>60</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>138</v>
+        <v>135</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="68.099999999999994" customHeight="1" x14ac:dyDescent="0.15">
@@ -1552,10 +1730,10 @@
         <v>66</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="H5" s="4" t="s">
         <v>134</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="68.099999999999994" customHeight="1" x14ac:dyDescent="0.15">
@@ -1578,10 +1756,10 @@
         <v>71</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>141</v>
+        <v>136</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="68.099999999999994" customHeight="1" x14ac:dyDescent="0.15">
@@ -1604,10 +1782,10 @@
         <v>76</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>137</v>
+        <v>134</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="68.099999999999994" customHeight="1" x14ac:dyDescent="0.15">
@@ -1767,6 +1945,12 @@
       <c r="F14" s="3" t="s">
         <v>108</v>
       </c>
+      <c r="G14" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>139</v>
+      </c>
     </row>
     <row r="15" spans="1:8" ht="68.099999999999994" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="2">
@@ -1786,6 +1970,12 @@
       </c>
       <c r="F15" s="3" t="s">
         <v>113</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="68.099999999999994" customHeight="1" x14ac:dyDescent="0.15">

--- a/PythonScript/EEG算法测试清单.xlsx
+++ b/PythonScript/EEG算法测试清单.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="27945" windowHeight="12255" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="在线算法" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="154">
   <si>
     <t>序号</t>
   </si>
@@ -569,6 +569,69 @@
       </rPr>
       <t>）具备去伪迹效果</t>
     </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>是</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>是</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>可行（先行滤波0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.5-30数据模拟，gamma频段显示极低能量排布</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>可行（用原始和滤波后5-20数据模拟，查看实时频谱处理效果</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）能够计算不同通带数据</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>可行 （高通5查看效果可行）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>可行 （凹陷50查看效果可行）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>可行 （低通20查看效果可行）</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -673,6 +736,277 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>123824</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>4480</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>23287</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="图片 1"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="16506824" y="385480"/>
+          <a:ext cx="6757463" cy="2567270"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>57150</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>490226</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>277628</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>153248</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="图片 2"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="16440150" y="6014726"/>
+          <a:ext cx="2277878" cy="1377522"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>276224</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>508461</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>401449</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>124678</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="图片 3"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="18716624" y="6032961"/>
+          <a:ext cx="2182625" cy="1330717"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>513516</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>466724</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>68081</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>137833</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="图片 4"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="21011316" y="5991224"/>
+          <a:ext cx="2297765" cy="1385609"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>526662</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>333942</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>115143</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="图片 5"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="23469600" y="6051162"/>
+          <a:ext cx="2162742" cy="1302981"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>447324</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>544514</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>786</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="图片 6"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="16421100" y="5114574"/>
+          <a:ext cx="2563814" cy="1267962"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>127800</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>443647</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>363439</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>809624</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="图片 7"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="19920750" y="5110897"/>
+          <a:ext cx="2293039" cy="1223227"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -1057,15 +1391,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
+      <xdr:colOff>114301</xdr:colOff>
       <xdr:row>13</xdr:row>
       <xdr:rowOff>745340</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>439209</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>248409</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>152401</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>169704</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1082,8 +1416,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="16497300" y="11413340"/>
-          <a:ext cx="1696509" cy="1217569"/>
+          <a:off x="17754601" y="11413340"/>
+          <a:ext cx="2781300" cy="1996114"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1389,6 +1723,7 @@
     <col min="4" max="4" width="52" customWidth="1"/>
     <col min="5" max="5" width="36" customWidth="1"/>
     <col min="6" max="6" width="48" customWidth="1"/>
+    <col min="8" max="8" width="34.125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.15">
@@ -1436,6 +1771,12 @@
       <c r="F2" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="G2" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>151</v>
+      </c>
     </row>
     <row r="3" spans="1:8" ht="68.099999999999994" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="2">
@@ -1456,6 +1797,12 @@
       <c r="F3" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="G3" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>153</v>
+      </c>
     </row>
     <row r="4" spans="1:8" ht="68.099999999999994" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="2">
@@ -1476,6 +1823,12 @@
       <c r="F4" s="3" t="s">
         <v>20</v>
       </c>
+      <c r="G4" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>152</v>
+      </c>
     </row>
     <row r="5" spans="1:8" ht="68.099999999999994" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="2">
@@ -1565,6 +1918,12 @@
       <c r="F8" s="3" t="s">
         <v>41</v>
       </c>
+      <c r="G8" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>150</v>
+      </c>
     </row>
     <row r="9" spans="1:8" ht="68.099999999999994" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="2">
@@ -1585,10 +1944,18 @@
       <c r="F9" s="3" t="s">
         <v>46</v>
       </c>
+      <c r="G9" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>149</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
